--- a/04_DESIGN_TABLES/DesignTable_5406P_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5406P_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,53 +609,53 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5406-20P</t>
+          <t>5406-08P</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.47</v>
+        <v>0.96</v>
       </c>
       <c r="C3" t="n">
-        <v>1.01036</v>
+        <v>0.50807</v>
       </c>
       <c r="D3" t="n">
-        <v>1.75</v>
+        <v>0.88</v>
       </c>
       <c r="E3" t="n">
-        <v>0.81335</v>
+        <v>0.40779</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7068</v>
+        <v>0.5337</v>
       </c>
       <c r="G3" t="n">
         <v>1.7899</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2632</v>
+        <v>0.2163</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6267</v>
+        <v>0.81557</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7068</v>
+        <v>0.5337</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.81335</v>
+        <v>0.40779</v>
       </c>
       <c r="M3" t="n">
-        <v>0.74378</v>
+        <v>0.35064</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>5406-20P</t>
+          <t>5406-08P</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Male Pipe Plug (NPTF), 1 1/4-11 1/2 NPTF</t>
+          <t>Male Pipe Plug (NPTF), 1/2-14 NPTF</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -683,62 +683,67 @@
           <t>Air-Way s88 only (double-pass 9 rows) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); solid hex head plug, hex head to a plain flat face, end chamfers NOT modelled</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-18: BUILD - the DROP above is void: OMi sells 5406-P-08 (alias of this Air-Way row, A4) | Brennan TFA p.67 TFA-p067-t03 row 5406-P-08: L2@DRIVE Air-Way 0.96 vs Brennan L LGTH 0.960: equal; C2HEX@HEX Air-Way 0.88 vs Brennan C HEX 0.875: rounding only</t>
+        </is>
+      </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>5406-P-20</t>
+          <t>5406-P-08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5406-24P</t>
+          <t>5406-12P</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.57</v>
+        <v>1.05</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1547</v>
+        <v>0.65241</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1.13</v>
       </c>
       <c r="E4" t="n">
-        <v>0.93283</v>
+        <v>0.51241</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7235</v>
+        <v>0.5457</v>
       </c>
       <c r="G4" t="n">
         <v>1.7899</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2765</v>
+        <v>0.2043</v>
       </c>
       <c r="I4" t="n">
-        <v>1.86566</v>
+        <v>1.02482</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7235</v>
+        <v>0.5457</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.93283</v>
+        <v>0.51241</v>
       </c>
       <c r="M4" t="n">
-        <v>0.86326</v>
+        <v>0.45527</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>5406-24P</t>
+          <t>5406-12P</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Male Pipe Plug (NPTF), 1 1/2-11 1/2 NPTF</t>
+          <t>Male Pipe Plug (NPTF), 3/4-14 NPTF</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -748,7 +753,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -766,92 +771,527 @@
           <t>Air-Way s88 only (double-pass 9 rows) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); solid hex head plug, hex head to a plain flat face, end chamfers NOT modelled</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-18: BUILD - the DROP above is void: OMi sells 5406-P-12 (alias of this Air-Way row, A4) | Brennan TFA p.67 TFA-p067-t03 row 5406-P-12: L2@DRIVE Air-Way 1.05 vs Brennan L LGTH 1.170: DIFFERS (Air-Way kept, s6); C2HEX@HEX Air-Way 1.13 vs Brennan C HEX 1.125: rounding only</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>5406-P-24</t>
+          <t>5406-P-12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5406-32P</t>
+          <t>5406-20P</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.01036</v>
+      </c>
+      <c r="D5" t="n">
         <v>1.75</v>
       </c>
-      <c r="C5" t="n">
-        <v>1.44338</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.5</v>
-      </c>
       <c r="E5" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="G5" t="n">
         <v>1.7899</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2735</v>
+        <v>0.2632</v>
       </c>
       <c r="I5" t="n">
-        <v>2.33859</v>
+        <v>1.6267</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="K5" t="n">
         <v>0.08696</v>
       </c>
       <c r="L5" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5406-20P</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Male Pipe Plug (NPTF), 1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>5406P</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>plug head</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Air-Way s88 only (double-pass 9 rows) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); solid hex head plug, hex head to a plain flat face, end chamfers NOT modelled</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>5406-P-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5406-24P</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5406-24P</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Male Pipe Plug (NPTF), 1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5406P</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>plug head</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Air-Way s88 only (double-pass 9 rows) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); solid hex head plug, hex head to a plain flat face, end chamfers NOT modelled</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>5406-P-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5406-32P</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.44338</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E7" t="n">
         <v>1.16929</v>
       </c>
-      <c r="M5" t="n">
+      <c r="F7" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="M7" t="n">
         <v>1.09973</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>5406-32P</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Male Pipe Plug (NPTF), 2-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>5406P</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>plug head</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Air-Way s88 only (double-pass 9 rows) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); solid hex head plug, hex head to a plain flat face, end chamfers NOT modelled</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>5406-P-32</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5406-P-02</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.25288</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.19657</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1161</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.03704</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.19657</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.16694</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5406-P-02</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Male Pipe Plug (NPTF), 1/8-27 NPTF</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>5406P</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1/8-27 NPTF</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>plug head</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L2@DRIVE: Brennan TFA catalog p67 table TFA-p067-t03 (EXTERNAL HEX PIPE PLUG) row 5406-P-02 column 'L LGTH' = 0.562 (catalog_verified.json); OMi Items row 1416: no dimension; Air-Way prints this size only as 5406-02P (review row, DROP; alias = Q-NEW-AWALIAS, open) = 0.56, rounding-only equal; 2026-10-02 proposal used the Air-Way alias value 0.56 - Brennan as printed is used here (alias not settled); C2HEX@HEX: Brennan TFA catalog p67 table TFA-p067-t03 (EXTERNAL HEX PIPE PLUG) row 5406-P-02 column 'C HEX' = 0.438 (catalog_verified.json); OMi Items row 1416: no dimension; Air-Way prints this size only as 5406-02P (review row, DROP; alias = Q-NEW-AWALIAS, open) = 0.44, rounding-only equal; 2026-10-02 proposal used the Air-Way alias value 0.44 - Brennan as printed is used here (alias not settled); THDMAJ_A@DRIVE: ASME B1.20.1 / B1.20.3 1/8 NPT basic dimensions = tools_new/generators/ms51500.NPTF[2] pipe OD (= alias row 5406-02P 0.405); equals the 2026-10-02 proposal; $PRP@Threads: ASME B1.20.1 / B1.20.3 1/8 NPT basic dimensions = tools_new/generators/ms51500.NPTF[2] thread text, format of the 5406P rows; equals the 2026-10-02 proposal | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); solid hex head plug, hex head to a plain flat face, end chamfers NOT modelled</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): L2 / hex from the Brennan TFA catalog alone (Air-Way alias 5406-02P agrees to rounding; alias not yet confirmed - Q-NEW-AWALIAS)</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>5406-P-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5406-P-04</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1582</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5406-P-04</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Male Pipe Plug (NPTF), 1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5406P</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>plug head</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L2@DRIVE: Brennan TFA catalog p67 table TFA-p067-t03 (EXTERNAL HEX PIPE PLUG) row 5406-P-04 column 'L LGTH' = 0.750 (catalog_verified.json); OMi Items row 1417: no dimension; Air-Way prints this size only as 5406-04P (review row, DROP; alias = Q-NEW-AWALIAS, open) = 0.75, rounding-only equal; 2026-10-02 proposal used the Air-Way alias value 0.75 - Brennan as printed is used here (alias not settled); C2HEX@HEX: Brennan TFA catalog p67 table TFA-p067-t03 (EXTERNAL HEX PIPE PLUG) row 5406-P-04 column 'C HEX' = 0.562 (catalog_verified.json); OMi Items row 1417: no dimension; Air-Way prints this size only as 5406-04P (review row, DROP; alias = Q-NEW-AWALIAS, open) = 0.56, rounding-only equal; 2026-10-02 proposal used the Air-Way alias value 0.56 - Brennan as printed is used here (alias not settled); THDMAJ_A@DRIVE: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] pipe OD (= alias row 5406-04P 0.54); equals the 2026-10-02 proposal; $PRP@Threads: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] thread text, format of the 5406P rows; equals the 2026-10-02 proposal | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); solid hex head plug, hex head to a plain flat face, end chamfers NOT modelled</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): L2 / hex from the Brennan TFA catalog alone (Air-Way alias 5406-04P agrees to rounding; alias not yet confirmed - Q-NEW-AWALIAS)</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>5406-P-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5406-P-06</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5406-P-06</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Male Pipe Plug (NPTF), 3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5406P</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>plug head</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L2@DRIVE: Brennan TFA catalog p67 table TFA-p067-t03 (EXTERNAL HEX PIPE PLUG) row 5406-P-06 column 'L LGTH' = 0.780 (catalog_verified.json); OMi Items row 1418: no dimension; Air-Way prints this size only as 5406-06P (review row, DROP; alias = Q-NEW-AWALIAS, open) = 0.78, rounding-only equal; 2026-10-02 proposal used the Air-Way alias value 0.78 - Brennan as printed is used here (alias not settled); C2HEX@HEX: Brennan TFA catalog p67 table TFA-p067-t03 (EXTERNAL HEX PIPE PLUG) row 5406-P-06 column 'C HEX' = 0.688 (catalog_verified.json); OMi Items row 1418: no dimension; Air-Way prints this size only as 5406-06P (review row, DROP; alias = Q-NEW-AWALIAS, open) = 0.69, rounding-only equal; 2026-10-02 proposal used the Air-Way alias value 0.69 - Brennan as printed is used here (alias not settled); THDMAJ_A@DRIVE: ASME B1.20.1 / B1.20.3 3/8 NPT basic dimensions = tools_new/generators/ms51500.NPTF[6] pipe OD (= alias row 5406-06P 0.675); equals the 2026-10-02 proposal; $PRP@Threads: ASME B1.20.1 / B1.20.3 3/8 NPT basic dimensions = tools_new/generators/ms51500.NPTF[6] thread text, format of the 5406P rows; equals the 2026-10-02 proposal | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); solid hex head plug, hex head to a plain flat face, end chamfers NOT modelled</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): L2 / hex from the Brennan TFA catalog alone (Air-Way alias 5406-06P agrees to rounding; alias not yet confirmed - Q-NEW-AWALIAS)</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>5406-P-06</t>
         </is>
       </c>
     </row>
